--- a/workpaper_templates/WP15_Fixed_Asset_Movement_Schedule.xlsx
+++ b/workpaper_templates/WP15_Fixed_Asset_Movement_Schedule.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]-#,##0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +59,17 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +104,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,20 +207,58 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -564,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -705,257 +761,318 @@
       <c r="A6" s="8" t="inlineStr"/>
       <c r="B6" s="8" t="inlineStr"/>
       <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="10">
+        <f>E6+F6-G6-H6</f>
+        <v/>
+      </c>
       <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="8" t="inlineStr"/>
       <c r="B7" s="8" t="inlineStr"/>
       <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="10">
+        <f>E7+F7-G7-H7</f>
+        <v/>
+      </c>
       <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
       <c r="B8" s="8" t="inlineStr"/>
       <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="10">
+        <f>E8+F8-G8-H8</f>
+        <v/>
+      </c>
       <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="8" t="inlineStr"/>
       <c r="B9" s="8" t="inlineStr"/>
       <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="10">
+        <f>E9+F9-G9-H9</f>
+        <v/>
+      </c>
       <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
       <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="10">
+        <f>E10+F10-G10-H10</f>
+        <v/>
+      </c>
       <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="8" t="inlineStr"/>
       <c r="B11" s="8" t="inlineStr"/>
       <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="10">
+        <f>E11+F11-G11-H11</f>
+        <v/>
+      </c>
       <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
       <c r="B12" s="8" t="inlineStr"/>
       <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="10">
+        <f>E12+F12-G12-H12</f>
+        <v/>
+      </c>
       <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="8" t="inlineStr"/>
       <c r="B13" s="8" t="inlineStr"/>
       <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="10">
+        <f>E13+F13-G13-H13</f>
+        <v/>
+      </c>
       <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
       <c r="B14" s="8" t="inlineStr"/>
       <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="10">
+        <f>E14+F14-G14-H14</f>
+        <v/>
+      </c>
       <c r="J14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="8" t="inlineStr"/>
       <c r="B15" s="8" t="inlineStr"/>
       <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="10">
+        <f>E15+F15-G15-H15</f>
+        <v/>
+      </c>
       <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
       <c r="B16" s="8" t="inlineStr"/>
       <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="10">
+        <f>E16+F16-G16-H16</f>
+        <v/>
+      </c>
       <c r="J16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="8" t="inlineStr"/>
       <c r="B17" s="8" t="inlineStr"/>
       <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="10">
+        <f>E17+F17-G17-H17</f>
+        <v/>
+      </c>
       <c r="J17" s="8" t="inlineStr"/>
     </row>
-    <row r="18" ht="6" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr"/>
+      <c r="C18" s="11" t="inlineStr"/>
+      <c r="D18" s="12">
+        <f>SUM(D6:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>SUM(E6:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>SUM(F6:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="12">
+        <f>SUM(G6:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="12">
+        <f>SUM(H6:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="12">
+        <f>SUM(I6:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="6" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>B.  DEPRECIATION RECONCILIATION</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Total depreciation per asset register</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Depreciation per accounts</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B24" s="15">
+        <f>B22-B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="8" t="inlineStr"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="6" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="8" t="inlineStr"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
@@ -964,282 +1081,324 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26" ht="6" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>C.  DISPOSALS</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Date Disposed</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>WDV at Disposal</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Proceeds</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Gain / (Loss)</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Tax Treatment</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr"/>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="8" t="inlineStr"/>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="8" t="inlineStr"/>
       <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="10">
+        <f>C29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="15">
+        <f>F29-E29</f>
+        <v/>
+      </c>
       <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="8" t="inlineStr"/>
       <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="10">
+        <f>C30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="9" t="inlineStr"/>
+      <c r="G30" s="15">
+        <f>F30-E30</f>
+        <v/>
+      </c>
       <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="8" t="inlineStr"/>
       <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="8" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="10">
+        <f>C31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="15">
+        <f>F31-E31</f>
+        <v/>
+      </c>
       <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="8" t="inlineStr"/>
       <c r="B32" s="8" t="inlineStr"/>
-      <c r="C32" s="8" t="inlineStr"/>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="10">
+        <f>C32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="15">
+        <f>F32-E32</f>
+        <v/>
+      </c>
       <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-    </row>
-    <row r="33" ht="6" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="10">
+        <f>C33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="15">
+        <f>F33-E33</f>
+        <v/>
+      </c>
+      <c r="H33" s="8" t="inlineStr"/>
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34" ht="6" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>D.  NOTES</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="8" t="inlineStr"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="11" t="n"/>
-    </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="8" t="inlineStr"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="11" t="n"/>
+      <c r="A36" s="16" t="inlineStr"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="18" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="8" t="inlineStr"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="11" t="n"/>
+      <c r="A37" s="16" t="inlineStr"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="18" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="8" t="inlineStr"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
-      <c r="J38" s="11" t="n"/>
-    </row>
-    <row r="39" ht="6" customHeight="1">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="18" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="16" t="inlineStr"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="18" t="n"/>
+    </row>
+    <row r="40" ht="6" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>SIGN-OFF</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>{{preparer}}</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G42" s="21" t="inlineStr">
         <is>
           <t>{{date_prepared}}</t>
         </is>
       </c>
-      <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>{{reviewer}}</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>{{date_reviewed}}</t>
         </is>
       </c>
-      <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr"/>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="15" t="n"/>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
-      <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
+      <c r="B44" s="22" t="inlineStr"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1248,19 +1407,27 @@
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A36:J36"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="B44:J44"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A20:J20"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="A41:J41"/>
     <mergeCell ref="G42:J42"/>
   </mergeCells>
+  <conditionalFormatting sqref="G29:G33">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>